--- a/apps/trainer/qwen3_fte/output/按8类拆分数据集/法兰分布统计.xlsx
+++ b/apps/trainer/qwen3_fte/output/按8类拆分数据集/法兰分布统计.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C188"/>
+  <dimension ref="A1:C189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1301</v>
+        <v>1274</v>
       </c>
       <c r="C2" t="n">
-        <v>18.04</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="3">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>896</v>
+        <v>861</v>
       </c>
       <c r="C3" t="n">
-        <v>12.42</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="4">
@@ -482,150 +482,150 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>647</v>
+        <v>622</v>
       </c>
       <c r="C4" t="n">
-        <v>8.970000000000001</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>承插焊法兰;SW;RF</t>
+          <t>盲板法兰;RF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>436</v>
+        <v>609</v>
       </c>
       <c r="C5" t="n">
-        <v>6.04</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>盲法兰;RF</t>
+          <t>承插焊法兰;RF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>307</v>
+        <v>513</v>
       </c>
       <c r="C6" t="n">
-        <v>4.26</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>法兰盖;RF</t>
+          <t>8字盲板;RF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>401</v>
       </c>
       <c r="C7" t="n">
-        <v>3.94</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8字盲板;RF</t>
+          <t>法兰;RJ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>法兰;RJ</t>
+          <t>带颈对焊法兰;RJ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C9" t="n">
-        <v>2.72</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>带颈对焊法兰;RJ</t>
+          <t>螺纹法兰;FNPT;RF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>183</v>
+        <v>124</v>
       </c>
       <c r="C10" t="n">
-        <v>2.54</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>带颈对焊法兰</t>
+          <t>带颈对焊法兰;RF|SERRATED</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="C11" t="n">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>螺纹法兰;FNPT;RF</t>
+          <t>8字盲板</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8字盲板;FF</t>
+          <t>带颈对焊法兰</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C13" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>盲法兰</t>
+          <t>8字盲板;FF</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C14" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>承插焊法兰;RF</t>
+          <t>盲板法兰</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C15" t="n">
         <v>0.9399999999999999</v>
@@ -634,14 +634,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>承插焊法兰;SW</t>
+          <t>盲板法兰;RJ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C16" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17">
@@ -654,30 +654,30 @@
         <v>56</v>
       </c>
       <c r="C17" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>带颈对焊法兰;LM</t>
+          <t>对焊法兰;RF</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C18" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>带颈平焊法兰</t>
+          <t>带颈对焊法兰;LM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C19" t="n">
         <v>0.73</v>
@@ -693,7 +693,7 @@
         <v>53</v>
       </c>
       <c r="C20" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="21">
@@ -703,319 +703,319 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8字盲板</t>
+          <t>承插焊法兰;RJ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>承插焊法兰;SW;RJ</t>
+          <t>承插焊法兰</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C23" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8字盲板;RJ</t>
+          <t>松套法兰;RF</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C24" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>松套法兰;RF</t>
+          <t>带颈平焊夹套法兰;RF</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>带颈平焊夹套法兰;RF</t>
+          <t>承插焊法兰;LM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C26" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>盲法兰;RJ</t>
+          <t>8字盲板;RJ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C27" t="n">
-        <v>0.54</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>法兰盖</t>
+          <t>法兰</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>承插焊法兰;SW;LM</t>
+          <t>带颈对焊法兰;RTJ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>螺纹法兰;NPT;RF</t>
+          <t>带颈平焊法兰;RJ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>法兰</t>
+          <t>插板;FF</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C31" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>带颈平焊法兰;RJ</t>
+          <t>带颈平焊法兰;LM</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>插板;FF</t>
+          <t>插板;RF</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C33" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>带颈平焊法兰;LM</t>
+          <t>法兰;FF</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C34" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>带颈对焊法兰;RTJ</t>
+          <t>松套法兰;FF</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C35" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>插板;RF</t>
+          <t>衬里法兰;RF</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C36" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>衬里法兰;RF</t>
+          <t>松套法兰;RJ</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>24</v>
       </c>
       <c r="C37" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>螺纹法兰;THD;RF</t>
+          <t>松套法兰;RTJ</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>24</v>
       </c>
       <c r="C38" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>法兰;FF</t>
+          <t>带颈对焊法兰;FF</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>松套法兰;FF</t>
+          <t>螺纹法兰;FNPT;RTJ</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>松套法兰;RJ</t>
+          <t>螺纹法兰;RF</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C41" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>松套法兰;RTJ</t>
+          <t>带颈平焊法兰</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C42" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>带颈对焊法兰;FF</t>
+          <t>螺纹法兰;FNPT;MFM</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>21</v>
       </c>
       <c r="C43" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>带颈对焊法兰;MFM</t>
+          <t>盲板法兰;RF|SERRATED</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C44" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>法兰盖;RJ</t>
+          <t>带颈对焊法兰;MFM</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C45" t="n">
         <v>0.25</v>
@@ -1024,11 +1024,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>孔板对焊法兰;RF</t>
+          <t>承插焊法兰;RF|SERRATED</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C46" t="n">
         <v>0.25</v>
@@ -1037,11 +1037,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>螺纹法兰;FNPT;RTJ</t>
+          <t>8字盲板;FRJ</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C47" t="n">
         <v>0.25</v>
@@ -1050,11 +1050,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>带颈平焊夹套法兰;RJ</t>
+          <t>螺纹法兰;FNPT;RJ</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C48" t="n">
         <v>0.25</v>
@@ -1063,11 +1063,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>带颈平焊夹套法兰;RTJ</t>
+          <t>带颈平焊夹套法兰;RJ</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C49" t="n">
         <v>0.25</v>
@@ -1076,24 +1076,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>带颈平焊夹套法兰;MFM</t>
+          <t>带颈对焊夹套法兰;RJ</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>18</v>
       </c>
       <c r="C50" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>带颈对焊法兰;FLRJ</t>
+          <t>螺纹法兰;FNPT;LF</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C51" t="n">
         <v>0.24</v>
@@ -1102,11 +1102,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>带颈对焊法兰;LF</t>
+          <t>螺纹法兰;FNPT;FF</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C52" t="n">
         <v>0.24</v>
@@ -1115,11 +1115,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>带颈对焊夹套法兰;RJ</t>
+          <t>螺纹法兰;FNPT;LM</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C53" t="n">
         <v>0.24</v>
@@ -1128,11 +1128,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>带颈平焊夹套法兰;LM</t>
+          <t>带颈平焊夹套法兰;RTJ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C54" t="n">
         <v>0.24</v>
@@ -1141,11 +1141,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>带颈平焊夹套法兰;LF</t>
+          <t>带颈平焊夹套法兰;MFM</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C55" t="n">
         <v>0.24</v>
@@ -1154,11 +1154,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>插板;RJ</t>
+          <t>带颈对焊法兰;FLRJ</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C56" t="n">
         <v>0.22</v>
@@ -1167,11 +1167,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>带颈对焊夹套法兰;MFM</t>
+          <t>带颈对焊法兰;LF</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C57" t="n">
         <v>0.22</v>
@@ -1180,11 +1180,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>螺纹法兰;MNPT;RTJ</t>
+          <t>带颈平焊夹套法兰;LM</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C58" t="n">
         <v>0.22</v>
@@ -1193,11 +1193,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>螺纹法兰;FNPT;MFM</t>
+          <t>带颈平焊夹套法兰;LF</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C59" t="n">
         <v>0.22</v>
@@ -1206,50 +1206,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>螺纹法兰;MNPT;LM</t>
+          <t>插板;RJ</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>法兰;MFM</t>
+          <t>带颈对焊夹套法兰;MFM</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>带颈对焊夹套法兰;RTJ</t>
+          <t>螺纹法兰;MNPT;RTJ</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>螺纹法兰;FNPT;RJ</t>
+          <t>螺纹法兰;MNPT;LM</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" t="n">
         <v>0.21</v>
@@ -1258,11 +1258,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>带颈对焊夹套法兰;LM</t>
+          <t>法兰;MFM</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C64" t="n">
         <v>0.21</v>
@@ -1271,11 +1271,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>带颈对焊夹套法兰;LF</t>
+          <t>带颈对焊夹套法兰;RTJ</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C65" t="n">
         <v>0.21</v>
@@ -1284,59 +1284,59 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>夹套盲法兰;RF</t>
+          <t>盲板法兰;FF</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>15</v>
       </c>
       <c r="C66" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>螺纹法兰;FNPT;LF</t>
+          <t>带颈对焊夹套法兰;LM</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C67" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>螺纹法兰;MNPT;RF</t>
+          <t>带颈对焊夹套法兰;LF</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>螺纹法兰;FNPT;FF</t>
+          <t>夹套盲法兰;RF</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C69" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>螺纹法兰;MNPT;MFM</t>
+          <t>带颈平焊法兰;FLRF</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1349,7 +1349,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>螺纹法兰;FNPT;LM</t>
+          <t>螺纹法兰;MNPT;RF</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1362,7 +1362,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>螺纹法兰;MNPT;LF</t>
+          <t>螺纹法兰;MNPT;MFM</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1375,7 +1375,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>螺纹法兰;MNPT;FF</t>
+          <t>螺纹法兰;MNPT;LF</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1388,50 +1388,50 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>螺纹法兰;MNPT;RJ</t>
+          <t>螺纹法兰;MNPT;FF</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C74" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>法兰;LF</t>
+          <t>螺纹法兰;MNPT;RJ</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>13</v>
       </c>
       <c r="C75" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>插板;RTJ</t>
+          <t>法兰;LF</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>13</v>
       </c>
       <c r="C76" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>法兰盖;FF</t>
+          <t>插板;RTJ</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C77" t="n">
         <v>0.17</v>
@@ -1440,228 +1440,228 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>插板;MFM</t>
+          <t>带颈平焊法兰;LF</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>12</v>
       </c>
       <c r="C78" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>插板;LM</t>
+          <t>插板;MFM</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>12</v>
       </c>
       <c r="C79" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>插板;LF</t>
+          <t>插板;LM</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>12</v>
       </c>
       <c r="C80" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>板式平焊法兰;FF</t>
+          <t>插板;LF</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>12</v>
       </c>
       <c r="C81" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>板式平焊法兰;RJ</t>
+          <t>板式平焊法兰;FF</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>12</v>
       </c>
       <c r="C82" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>板式平焊法兰;RTJ</t>
+          <t>板式平焊法兰;RJ</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>12</v>
       </c>
       <c r="C83" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>衬里法兰;FF</t>
+          <t>板式平焊法兰;RTJ</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>12</v>
       </c>
       <c r="C84" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>衬里法兰;RJ</t>
+          <t>衬里法兰;FF</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>12</v>
       </c>
       <c r="C85" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>孔板对焊法兰;RJ</t>
+          <t>衬里法兰;RJ</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>12</v>
       </c>
       <c r="C86" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>孔板对焊法兰;RTJ</t>
+          <t>孔板对焊法兰;RF</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>12</v>
       </c>
       <c r="C87" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>异径法兰;RJ</t>
+          <t>孔板对焊法兰;RJ</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>12</v>
       </c>
       <c r="C88" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>异径法兰;RTJ</t>
+          <t>孔板对焊法兰;RTJ</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>12</v>
       </c>
       <c r="C89" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>异径法兰;LM</t>
+          <t>异径法兰;RTJ</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>12</v>
       </c>
       <c r="C90" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>夹套盲法兰;FF</t>
+          <t>异径法兰;LM</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>12</v>
       </c>
       <c r="C91" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>夹套盲法兰;RJ</t>
+          <t>夹套盲法兰;FF</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>12</v>
       </c>
       <c r="C92" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>夹套盲法兰;RTJ</t>
+          <t>夹套盲法兰;RJ</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>12</v>
       </c>
       <c r="C93" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>法兰;RTJ</t>
+          <t>夹套盲法兰;RTJ</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C94" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>板式平焊法兰;MFM</t>
+          <t>法兰;RTJ</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1674,7 +1674,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>板式平焊法兰;LM</t>
+          <t>板式平焊法兰;MFM</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1687,7 +1687,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>板式平焊法兰;LF</t>
+          <t>板式平焊法兰;LM</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1700,7 +1700,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>异径法兰;RF</t>
+          <t>板式平焊法兰;LF</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1726,7 +1726,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>异径法兰;MFM</t>
+          <t>异径法兰;RJ</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1739,7 +1739,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>异径法兰;LF</t>
+          <t>夹套盲法兰;MFM</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1752,7 +1752,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>夹套盲法兰;MFM</t>
+          <t>夹套盲法兰;LM</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1765,7 +1765,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>夹套盲法兰;LM</t>
+          <t>夹套盲法兰;LF</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1778,163 +1778,163 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>夹套盲法兰;LF</t>
+          <t>盲板法兰;FLRF</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C104" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>带颈平焊法兰;LF</t>
+          <t>8字盲板;RF|SERRATED</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C105" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>承插焊法兰;SW;LF</t>
+          <t>盲板法兰;RTJ</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C106" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8字盲板;MFM</t>
+          <t>带颈平焊法兰;RF|SERRATED</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C107" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>对焊法兰;RF</t>
+          <t>盲板法兰;MFM</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C108" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>对焊法兰;LM</t>
+          <t>盲板法兰;LM</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C109" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>螺纹法兰;THD;RJ</t>
+          <t>盲板法兰;LF</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C110" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>螺纹法兰;THD;LM</t>
+          <t>异径法兰;RF</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C111" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>带颈平焊法兰;FF</t>
+          <t>异径法兰;MFM</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C112" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>带颈平焊法兰;RTJ</t>
+          <t>异径法兰;LF</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C113" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>带颈平焊法兰;MFM</t>
+          <t>带颈平焊法兰;FF</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C114" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>承插焊法兰;SW;FF</t>
+          <t>承插焊法兰;FF</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C115" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>承插焊法兰;SW;RTJ</t>
+          <t>承插焊法兰;LF</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -1947,7 +1947,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>承插焊法兰;SW;MFM</t>
+          <t>8字盲板;MFM</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -1960,7 +1960,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>法兰盖;RTJ</t>
+          <t>盲板法兰;FNPT;RF</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -1973,7 +1973,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>法兰盖;MFM</t>
+          <t>对焊法兰;LM</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -1986,7 +1986,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>法兰盖;LM</t>
+          <t>螺纹法兰;RJ</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -1999,7 +1999,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>法兰盖;LF</t>
+          <t>螺纹法兰;LM</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2012,7 +2012,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8字盲板;RTJ</t>
+          <t>带颈平焊法兰;RTJ</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2025,7 +2025,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8字盲板;LM</t>
+          <t>带颈平焊法兰;MFM</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2038,7 +2038,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8字盲板;LF</t>
+          <t>承插焊法兰;RTJ</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2051,7 +2051,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>对焊法兰;FF</t>
+          <t>承插焊法兰;MFM</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -2064,7 +2064,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>对焊法兰;RJ</t>
+          <t>盲板法兰;FNPT;FF</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2077,7 +2077,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>对焊法兰;RTJ</t>
+          <t>盲板法兰;FNPT;RJ</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2090,7 +2090,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>对焊法兰;MFM</t>
+          <t>8字盲板;RTJ</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2103,7 +2103,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>对焊法兰;LF</t>
+          <t>8字盲板;LM</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2116,176 +2116,176 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>盲法兰;NPT;RF</t>
+          <t>8字盲板;LF</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C130" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>螺纹法兰;THD;MFM</t>
+          <t>对焊法兰;FF</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>螺纹法兰;THD;FF</t>
+          <t>对焊法兰;RJ</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>松套法兰</t>
+          <t>对焊法兰;RTJ</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C133" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>螺纹法兰;THD;RTJ</t>
+          <t>对焊法兰;MFM</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C134" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>盲法兰;FNPT;RF</t>
+          <t>对焊法兰;LF</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C135" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>盲法兰;MNPT;RF</t>
+          <t>盲板法兰;FNPT;RTJ</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C136" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>盲法兰;FNPT;FF</t>
+          <t>盲板法兰;FNPT;MFM</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C137" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>盲法兰;MNPT;FF</t>
+          <t>盲板法兰;FNPT;LM</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C138" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>盲法兰;FNPT;RJ</t>
+          <t>盲板法兰;FNPT;LF</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C139" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>盲法兰;MNPT;RJ</t>
+          <t>松套法兰</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C140" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>盲法兰;FNPT;RTJ</t>
+          <t>螺纹法兰;MFM</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C141" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>盲法兰;MNPT;RTJ</t>
+          <t>螺纹法兰;FF</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C142" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>盲法兰;FNPT;MFM</t>
+          <t>板式平焊松套法兰;RF</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -2298,7 +2298,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>盲法兰;MNPT;MFM</t>
+          <t>螺纹法兰;RTJ</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -2311,7 +2311,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>盲法兰;FNPT;LM</t>
+          <t>盲板法兰;MNPT;RF</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -2324,7 +2324,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>盲法兰;MNPT;LM</t>
+          <t>盲板法兰;MNPT;FF</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -2337,7 +2337,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>盲法兰;FNPT;LF</t>
+          <t>盲板法兰;MNPT;RJ</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -2350,7 +2350,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>盲法兰;MNPT;LF</t>
+          <t>盲板法兰;MNPT;RTJ</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -2363,46 +2363,46 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>带颈对焊夹套法兰;FM</t>
+          <t>盲板法兰;MNPT;MFM</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C149" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>螺纹法兰;NPT;RTJ</t>
+          <t>盲板法兰;MNPT;LM</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C150" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>螺纹法兰;THD;LF</t>
+          <t>盲板法兰;MNPT;LF</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C151" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>螺纹法兰;NPT;MFM</t>
+          <t>带颈对焊法兰;FLRF</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -2415,163 +2415,163 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>螺纹法兰;NPT;FF</t>
+          <t>盲板法兰;FNPT;RF|SERRATED</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C153" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>螺纹法兰;NPT;LM</t>
+          <t>固定法兰;FF</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C154" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>螺纹法兰;NPT;RJ</t>
+          <t>带颈平焊法兰;M</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C155" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>螺纹法兰;NPT;LF</t>
+          <t>螺纹法兰;RF|SERRATED</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C156" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>带颈平焊法兰;LF|RF</t>
+          <t>孔板对焊法兰;SW;RF|SERRATED</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C157" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>插板</t>
+          <t>带颈对焊法兰;M</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C158" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>带颈对焊夹套法兰;M</t>
+          <t>螺纹法兰;LF</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C159" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>盲法兰;RTJ</t>
+          <t>带颈对焊夹套法兰;FM</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C160" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>法兰盖;FM</t>
+          <t>螺纹法兰</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C161" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>螺纹法兰;THD</t>
+          <t>固定法兰</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C162" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>盲法兰;THD;RF</t>
+          <t>插板</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C163" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>盲法兰;FF</t>
+          <t>异径夹套法兰;RF</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C164" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>盲法兰;NPT;FF</t>
+          <t>带颈对焊夹套法兰;M</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -2584,7 +2584,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>盲法兰;THD;FF</t>
+          <t>盲板法兰;FM</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -2597,7 +2597,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>盲法兰;NPT;RJ</t>
+          <t>夹套法兰;MF</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -2610,7 +2610,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>盲法兰;THD;RJ</t>
+          <t>夹套法兰;RJ</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -2623,7 +2623,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>盲法兰;NPT;RTJ</t>
+          <t>螺纹法兰;FNPT</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -2636,7 +2636,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>盲法兰;THD;RTJ</t>
+          <t>法兰;GROOVED;RF</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -2649,7 +2649,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>盲法兰;MFM</t>
+          <t>盲板法兰;THD;RF</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -2662,7 +2662,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>盲法兰;NPT;MFM</t>
+          <t>异径法兰;THD;RJ</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -2675,7 +2675,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>盲法兰;THD;MFM</t>
+          <t>盲板法兰;THD;FF</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -2688,7 +2688,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>盲法兰;LM</t>
+          <t>盲板法兰;THD;RJ</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -2701,7 +2701,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>盲法兰;NPT;LM</t>
+          <t>盲板法兰;THD;RTJ</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -2714,7 +2714,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>盲法兰;THD;LM</t>
+          <t>盲板法兰;THD;MFM</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -2727,7 +2727,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>盲法兰;LF</t>
+          <t>盲板法兰;THD;LM</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -2740,7 +2740,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>盲法兰;NPT;LF</t>
+          <t>盲板法兰;THD;LF</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -2753,20 +2753,20 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>盲法兰;THD;LF</t>
+          <t>盲板法兰;M</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C179" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>8字盲板;FWRF</t>
+          <t>带颈对焊夹套法兰</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -2779,7 +2779,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>法兰;SW;RJ</t>
+          <t>带颈对焊法兰;FM</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -2792,7 +2792,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>法兰盖;M</t>
+          <t>带颈平焊夹套法兰</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -2805,7 +2805,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>带颈对焊夹套法兰</t>
+          <t>孔板对焊法兰;RF|SERRATED</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -2818,7 +2818,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>带颈对焊法兰;FM</t>
+          <t>法兰;MF</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -2831,7 +2831,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>带颈对焊夹套法兰;MFM|RJ</t>
+          <t>异径板式法兰;RF</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -2844,7 +2844,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>螺纹法兰;FNPT</t>
+          <t>夹套法兰;RF</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -2857,7 +2857,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>螺纹法兰;NPT</t>
+          <t>异径法兰;THD;MFM</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -2870,13 +2870,26 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>螺纹法兰;RF</t>
+          <t>异径法兰;THD;RF</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>1</v>
       </c>
       <c r="C188" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>异径法兰;THD;LF</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -2891,7 +2904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2918,10 +2931,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1794</v>
+        <v>1837</v>
       </c>
       <c r="C2" t="n">
-        <v>24.87</v>
+        <v>24.29</v>
       </c>
     </row>
     <row r="3">
@@ -2931,10 +2944,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1040</v>
+        <v>1003</v>
       </c>
       <c r="C3" t="n">
-        <v>14.42</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="4">
@@ -2944,36 +2957,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>995</v>
+        <v>972</v>
       </c>
       <c r="C4" t="n">
-        <v>13.79</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>承插焊法兰</t>
+          <t>盲板法兰</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>686</v>
+        <v>942</v>
       </c>
       <c r="C5" t="n">
-        <v>9.51</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>盲法兰</t>
+          <t>承插焊法兰</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>550</v>
+        <v>695</v>
       </c>
       <c r="C6" t="n">
-        <v>7.63</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="7">
@@ -2983,10 +2996,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>684</v>
       </c>
       <c r="C7" t="n">
-        <v>5.71</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2996,88 +3009,88 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C8" t="n">
-        <v>5.7</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>法兰盖</t>
+          <t>带颈对焊夹套法兰</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>385</v>
+        <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>5.34</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>带颈对焊夹套法兰</t>
+          <t>带颈平焊夹套法兰</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C10" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>带颈平焊夹套法兰</t>
+          <t>板式平焊法兰</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C11" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>插板</t>
+          <t>松套法兰</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>板式平焊法兰</t>
+          <t>插板</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>120</v>
       </c>
       <c r="C13" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>松套法兰</t>
+          <t>对焊法兰</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C14" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="15">
@@ -3090,7 +3103,7 @@
         <v>84</v>
       </c>
       <c r="C15" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="16">
@@ -3100,49 +3113,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C16" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>对焊法兰</t>
+          <t>衬里法兰</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C17" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>衬里法兰</t>
+          <t>孔板对焊法兰</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C18" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>孔板对焊法兰</t>
+          <t>固定法兰</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>0.58</v>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>板式平焊松套法兰</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>夹套法兰</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>异径夹套法兰</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>异径板式法兰</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -3183,7 +3248,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7213</v>
+        <v>7562</v>
       </c>
       <c r="C2" t="n">
         <v>100</v>
@@ -3227,75 +3292,75 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6067</v>
+        <v>7089</v>
       </c>
       <c r="C2" t="n">
-        <v>84.11</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>FNPT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>619</v>
+        <v>304</v>
       </c>
       <c r="C3" t="n">
-        <v>8.58</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FNPT</t>
+          <t>MNPT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>223</v>
+        <v>143</v>
       </c>
       <c r="C4" t="n">
-        <v>3.09</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MNPT</t>
+          <t>THD</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>1.98</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>THD</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>1.12</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NPT</t>
+          <t>GROOVED</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1.11</v>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -3309,7 +3374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3336,10 +3401,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4615</v>
+        <v>4986</v>
       </c>
       <c r="C2" t="n">
-        <v>63.95</v>
+        <v>64.34</v>
       </c>
     </row>
     <row r="3">
@@ -3349,10 +3414,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="C3" t="n">
-        <v>10.5</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="4">
@@ -3362,10 +3427,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>482</v>
+        <v>388</v>
       </c>
       <c r="C4" t="n">
-        <v>6.68</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="5">
@@ -3378,7 +3443,7 @@
         <v>336</v>
       </c>
       <c r="C5" t="n">
-        <v>4.66</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="6">
@@ -3388,10 +3453,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="C6" t="n">
-        <v>4.41</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="7">
@@ -3401,10 +3466,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C7" t="n">
-        <v>3.59</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="8">
@@ -3417,7 +3482,7 @@
         <v>214</v>
       </c>
       <c r="C8" t="n">
-        <v>2.97</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="9">
@@ -3430,59 +3495,98 @@
         <v>206</v>
       </c>
       <c r="C9" t="n">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FLRJ</t>
+          <t>SERRATED</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="C10" t="n">
-        <v>0.24</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FM</t>
+          <t>FLRF</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>0.11</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>FRJ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FWRF</t>
+          <t>FLRJ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01</v>
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FM</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
